--- a/diseases/d007/1975-1979.xlsx
+++ b/diseases/d007/1975-1979.xlsx
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">

--- a/diseases/d007/1975-1979.xlsx
+++ b/diseases/d007/1975-1979.xlsx
@@ -2183,7 +2183,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
